--- a/Data/Janzen-Connell/SeedlingDATA2020_2024.xlsx
+++ b/Data/Janzen-Connell/SeedlingDATA2020_2024.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10916"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr autoCompressPictures="0" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/deirdre/Documents/github/coexistBCforests/Data/Janzen-Connell/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PhD\Project\coexistBCforests\Data\Janzen-Connell\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{721F040E-8931-8247-9A5B-1CED2898ACC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CD79A3A-0686-44AC-8FAD-944A645ECE92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-33860" yWindow="600" windowWidth="30480" windowHeight="19020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28905" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -298,11 +298,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -310,7 +310,7 @@
       <u/>
       <sz val="12"/>
       <color theme="10"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -318,8 +318,15 @@
       <u/>
       <sz val="12"/>
       <color theme="11"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -347,8 +354,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Followed Hyperlink" xfId="2" builtinId="9" hidden="1"/>
@@ -371,9 +381,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -411,7 +421,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -517,7 +527,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -659,7 +669,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -668,16 +678,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N373"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.07421875" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="4" max="5" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="11.5" customWidth="1"/>
-    <col min="9" max="9" width="7.33203125" customWidth="1"/>
-    <col min="10" max="10" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="11.4609375" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="11.4609375" customWidth="1"/>
+    <col min="9" max="9" width="7.3046875" customWidth="1"/>
+    <col min="10" max="10" width="12.69140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8" style="1"/>
     <col min="12" max="12" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -708,7 +719,7 @@
       <c r="J1" t="s">
         <v>4</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="L1" t="s">
@@ -718,7 +729,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -749,7 +760,7 @@
       <c r="J2" t="s">
         <v>9</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="1">
         <v>1</v>
       </c>
       <c r="L2" t="s">
@@ -759,7 +770,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -772,11 +783,11 @@
       <c r="E3">
         <v>0</v>
       </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="K3" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -801,14 +812,14 @@
       <c r="J4" t="s">
         <v>9</v>
       </c>
-      <c r="K4">
-        <v>1</v>
+      <c r="K4" s="1">
+        <v>0</v>
       </c>
       <c r="L4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -833,14 +844,14 @@
       <c r="J5" t="s">
         <v>9</v>
       </c>
-      <c r="K5">
-        <v>1</v>
+      <c r="K5" s="1">
+        <v>0</v>
       </c>
       <c r="L5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -853,11 +864,11 @@
       <c r="E6">
         <v>0</v>
       </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="K6" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -879,14 +890,14 @@
       <c r="J7" t="s">
         <v>9</v>
       </c>
-      <c r="K7">
-        <v>1</v>
+      <c r="K7" s="1">
+        <v>0</v>
       </c>
       <c r="L7" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -899,11 +910,11 @@
       <c r="E8">
         <v>0</v>
       </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="K8" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -925,14 +936,14 @@
       <c r="J9" t="s">
         <v>9</v>
       </c>
-      <c r="K9">
-        <v>1</v>
+      <c r="K9" s="1">
+        <v>0</v>
       </c>
       <c r="L9" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -945,11 +956,11 @@
       <c r="E10">
         <v>0</v>
       </c>
-      <c r="K10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="K10" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>7</v>
       </c>
@@ -962,11 +973,11 @@
       <c r="E11">
         <v>0</v>
       </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="K11" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -997,14 +1008,14 @@
       <c r="J12" t="s">
         <v>9</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="1">
         <v>1</v>
       </c>
       <c r="L12" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>7</v>
       </c>
@@ -1032,14 +1043,14 @@
       <c r="J13" t="s">
         <v>9</v>
       </c>
-      <c r="K13">
+      <c r="K13" s="1">
         <v>1</v>
       </c>
       <c r="L13" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>7</v>
       </c>
@@ -1067,14 +1078,14 @@
       <c r="J14" t="s">
         <v>9</v>
       </c>
-      <c r="K14">
-        <v>1</v>
+      <c r="K14" s="1">
+        <v>0</v>
       </c>
       <c r="L14" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>7</v>
       </c>
@@ -1102,14 +1113,14 @@
       <c r="J15" t="s">
         <v>9</v>
       </c>
-      <c r="K15">
+      <c r="K15" s="1">
         <v>1</v>
       </c>
       <c r="L15" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>7</v>
       </c>
@@ -1137,14 +1148,14 @@
       <c r="J16" t="s">
         <v>9</v>
       </c>
-      <c r="K16">
+      <c r="K16" s="1">
         <v>1</v>
       </c>
       <c r="L16" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>7</v>
       </c>
@@ -1166,14 +1177,14 @@
       <c r="J17" t="s">
         <v>9</v>
       </c>
-      <c r="K17">
-        <v>1</v>
+      <c r="K17" s="1">
+        <v>0</v>
       </c>
       <c r="L17" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>7</v>
       </c>
@@ -1204,14 +1215,14 @@
       <c r="J18" t="s">
         <v>9</v>
       </c>
-      <c r="K18">
+      <c r="K18" s="1">
         <v>1</v>
       </c>
       <c r="L18" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>7</v>
       </c>
@@ -1233,14 +1244,14 @@
       <c r="J19" t="s">
         <v>9</v>
       </c>
-      <c r="K19">
-        <v>1</v>
+      <c r="K19" s="1">
+        <v>0</v>
       </c>
       <c r="L19" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>7</v>
       </c>
@@ -1262,14 +1273,14 @@
       <c r="J20" t="s">
         <v>9</v>
       </c>
-      <c r="K20">
-        <v>1</v>
+      <c r="K20" s="1">
+        <v>0</v>
       </c>
       <c r="L20" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>7</v>
       </c>
@@ -1300,14 +1311,14 @@
       <c r="J21" t="s">
         <v>9</v>
       </c>
-      <c r="K21">
+      <c r="K21" s="1">
         <v>1</v>
       </c>
       <c r="L21" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>7</v>
       </c>
@@ -1338,14 +1349,14 @@
       <c r="J22" t="s">
         <v>9</v>
       </c>
-      <c r="K22">
+      <c r="K22" s="1">
         <v>1</v>
       </c>
       <c r="L22" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>7</v>
       </c>
@@ -1358,14 +1369,14 @@
       <c r="E23">
         <v>0</v>
       </c>
-      <c r="K23">
+      <c r="K23" s="1">
         <v>0</v>
       </c>
       <c r="N23" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>7</v>
       </c>
@@ -1378,11 +1389,11 @@
       <c r="E24">
         <v>0</v>
       </c>
-      <c r="K24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="K24" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>7</v>
       </c>
@@ -1404,14 +1415,14 @@
       <c r="J25" t="s">
         <v>9</v>
       </c>
-      <c r="K25">
-        <v>1</v>
+      <c r="K25" s="1">
+        <v>0</v>
       </c>
       <c r="L25" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>7</v>
       </c>
@@ -1442,7 +1453,7 @@
       <c r="J26" t="s">
         <v>9</v>
       </c>
-      <c r="K26">
+      <c r="K26" s="1">
         <v>1</v>
       </c>
       <c r="L26" t="s">
@@ -1452,7 +1463,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>7</v>
       </c>
@@ -1474,14 +1485,14 @@
       <c r="J27" t="s">
         <v>9</v>
       </c>
-      <c r="K27">
-        <v>1</v>
+      <c r="K27" s="1">
+        <v>0</v>
       </c>
       <c r="L27" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>7</v>
       </c>
@@ -1494,11 +1505,11 @@
       <c r="E28">
         <v>0</v>
       </c>
-      <c r="K28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="K28" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>7</v>
       </c>
@@ -1526,14 +1537,14 @@
       <c r="J29" t="s">
         <v>9</v>
       </c>
-      <c r="K29">
-        <v>1</v>
+      <c r="K29" s="1">
+        <v>0</v>
       </c>
       <c r="L29" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>7</v>
       </c>
@@ -1555,14 +1566,14 @@
       <c r="J30" t="s">
         <v>9</v>
       </c>
-      <c r="K30">
-        <v>1</v>
+      <c r="K30" s="1">
+        <v>0</v>
       </c>
       <c r="L30" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>7</v>
       </c>
@@ -1575,11 +1586,11 @@
       <c r="E31">
         <v>0</v>
       </c>
-      <c r="K31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="K31" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>7</v>
       </c>
@@ -1601,14 +1612,14 @@
       <c r="J32" t="s">
         <v>9</v>
       </c>
-      <c r="K32">
-        <v>1</v>
+      <c r="K32" s="1">
+        <v>0</v>
       </c>
       <c r="L32" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>7</v>
       </c>
@@ -1621,11 +1632,11 @@
       <c r="E33">
         <v>0</v>
       </c>
-      <c r="K33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="K33" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>7</v>
       </c>
@@ -1656,14 +1667,14 @@
       <c r="J34" t="s">
         <v>9</v>
       </c>
-      <c r="K34">
+      <c r="K34" s="1">
         <v>1</v>
       </c>
       <c r="L34" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>7</v>
       </c>
@@ -1676,11 +1687,11 @@
       <c r="E35">
         <v>0</v>
       </c>
-      <c r="K35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="K35" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>7</v>
       </c>
@@ -1693,11 +1704,11 @@
       <c r="E36">
         <v>0</v>
       </c>
-      <c r="K36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="K36" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>7</v>
       </c>
@@ -1728,14 +1739,14 @@
       <c r="J37" t="s">
         <v>9</v>
       </c>
-      <c r="K37">
+      <c r="K37" s="1">
         <v>1</v>
       </c>
       <c r="L37" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>7</v>
       </c>
@@ -1757,14 +1768,14 @@
       <c r="J38" t="s">
         <v>9</v>
       </c>
-      <c r="K38">
-        <v>1</v>
+      <c r="K38" s="1">
+        <v>0</v>
       </c>
       <c r="L38" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>7</v>
       </c>
@@ -1792,14 +1803,14 @@
       <c r="J39" t="s">
         <v>9</v>
       </c>
-      <c r="K39">
-        <v>1</v>
+      <c r="K39" s="1">
+        <v>0</v>
       </c>
       <c r="L39" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>7</v>
       </c>
@@ -1821,14 +1832,14 @@
       <c r="J40" t="s">
         <v>9</v>
       </c>
-      <c r="K40">
-        <v>1</v>
+      <c r="K40" s="1">
+        <v>0</v>
       </c>
       <c r="L40" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>7</v>
       </c>
@@ -1859,14 +1870,14 @@
       <c r="J41" t="s">
         <v>9</v>
       </c>
-      <c r="K41">
+      <c r="K41" s="1">
         <v>1</v>
       </c>
       <c r="L41" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>7</v>
       </c>
@@ -1897,7 +1908,7 @@
       <c r="J42" t="s">
         <v>9</v>
       </c>
-      <c r="K42">
+      <c r="K42" s="1">
         <v>1</v>
       </c>
       <c r="L42" t="s">
@@ -1907,7 +1918,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>7</v>
       </c>
@@ -1929,14 +1940,14 @@
       <c r="J43" t="s">
         <v>9</v>
       </c>
-      <c r="K43">
-        <v>1</v>
+      <c r="K43" s="1">
+        <v>0</v>
       </c>
       <c r="L43" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>7</v>
       </c>
@@ -1964,14 +1975,14 @@
       <c r="J44" t="s">
         <v>9</v>
       </c>
-      <c r="K44">
-        <v>1</v>
+      <c r="K44" s="1">
+        <v>0</v>
       </c>
       <c r="L44" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>7</v>
       </c>
@@ -1993,14 +2004,14 @@
       <c r="J45" t="s">
         <v>9</v>
       </c>
-      <c r="K45">
-        <v>1</v>
+      <c r="K45" s="1">
+        <v>0</v>
       </c>
       <c r="L45" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>7</v>
       </c>
@@ -2022,14 +2033,14 @@
       <c r="J46" t="s">
         <v>9</v>
       </c>
-      <c r="K46">
-        <v>1</v>
+      <c r="K46" s="1">
+        <v>0</v>
       </c>
       <c r="L46" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>7</v>
       </c>
@@ -2051,14 +2062,14 @@
       <c r="J47" t="s">
         <v>33</v>
       </c>
-      <c r="K47">
-        <v>1</v>
+      <c r="K47" s="1">
+        <v>0</v>
       </c>
       <c r="L47" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>7</v>
       </c>
@@ -2080,14 +2091,14 @@
       <c r="J48" t="s">
         <v>34</v>
       </c>
-      <c r="K48">
-        <v>1</v>
+      <c r="K48" s="1">
+        <v>0</v>
       </c>
       <c r="L48" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>7</v>
       </c>
@@ -2115,14 +2126,14 @@
       <c r="J49" t="s">
         <v>9</v>
       </c>
-      <c r="K49">
-        <v>0</v>
+      <c r="K49" s="1">
+        <v>1</v>
       </c>
       <c r="L49" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>7</v>
       </c>
@@ -2150,14 +2161,14 @@
       <c r="J50" t="s">
         <v>9</v>
       </c>
-      <c r="K50">
-        <v>1</v>
+      <c r="K50" s="1">
+        <v>0</v>
       </c>
       <c r="L50" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>7</v>
       </c>
@@ -2185,14 +2196,14 @@
       <c r="J51" t="s">
         <v>9</v>
       </c>
-      <c r="K51">
-        <v>1</v>
+      <c r="K51" s="1">
+        <v>0</v>
       </c>
       <c r="L51" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>7</v>
       </c>
@@ -2223,14 +2234,14 @@
       <c r="J52" t="s">
         <v>9</v>
       </c>
-      <c r="K52">
+      <c r="K52" s="1">
         <v>1</v>
       </c>
       <c r="L52" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>7</v>
       </c>
@@ -2261,14 +2272,14 @@
       <c r="J53" t="s">
         <v>9</v>
       </c>
-      <c r="K53">
+      <c r="K53" s="1">
         <v>1</v>
       </c>
       <c r="L53" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>7</v>
       </c>
@@ -2299,14 +2310,14 @@
       <c r="J54" t="s">
         <v>9</v>
       </c>
-      <c r="K54">
-        <v>1</v>
+      <c r="K54" s="1">
+        <v>0</v>
       </c>
       <c r="L54" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>7</v>
       </c>
@@ -2319,11 +2330,11 @@
       <c r="E55">
         <v>0</v>
       </c>
-      <c r="K55">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="K55" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>7</v>
       </c>
@@ -2345,14 +2356,14 @@
       <c r="J56" t="s">
         <v>9</v>
       </c>
-      <c r="K56">
-        <v>1</v>
+      <c r="K56" s="1">
+        <v>0</v>
       </c>
       <c r="L56" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>7</v>
       </c>
@@ -2374,14 +2385,14 @@
       <c r="J57" t="s">
         <v>9</v>
       </c>
-      <c r="K57">
-        <v>1</v>
+      <c r="K57" s="1">
+        <v>0</v>
       </c>
       <c r="L57" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>7</v>
       </c>
@@ -2403,14 +2414,14 @@
       <c r="J58" t="s">
         <v>33</v>
       </c>
-      <c r="K58">
-        <v>1</v>
+      <c r="K58" s="1">
+        <v>0</v>
       </c>
       <c r="L58" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>7</v>
       </c>
@@ -2441,7 +2452,7 @@
       <c r="J59" t="s">
         <v>9</v>
       </c>
-      <c r="K59">
+      <c r="K59" s="1">
         <v>1</v>
       </c>
       <c r="L59" t="s">
@@ -2451,7 +2462,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>7</v>
       </c>
@@ -2473,14 +2484,14 @@
       <c r="J60" t="s">
         <v>9</v>
       </c>
-      <c r="K60">
-        <v>1</v>
+      <c r="K60" s="1">
+        <v>0</v>
       </c>
       <c r="L60" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>7</v>
       </c>
@@ -2502,8 +2513,8 @@
       <c r="J61" t="s">
         <v>9</v>
       </c>
-      <c r="K61">
-        <v>1</v>
+      <c r="K61" s="1">
+        <v>0</v>
       </c>
       <c r="L61" t="s">
         <v>35</v>
@@ -2512,7 +2523,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>7</v>
       </c>
@@ -2543,14 +2554,14 @@
       <c r="J62" t="s">
         <v>9</v>
       </c>
-      <c r="K62">
+      <c r="K62" s="1">
         <v>1</v>
       </c>
       <c r="L62" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>7</v>
       </c>
@@ -2572,14 +2583,14 @@
       <c r="J63" t="s">
         <v>9</v>
       </c>
-      <c r="K63">
-        <v>1</v>
+      <c r="K63" s="1">
+        <v>0</v>
       </c>
       <c r="L63" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>7</v>
       </c>
@@ -2610,14 +2621,14 @@
       <c r="J64" t="s">
         <v>9</v>
       </c>
-      <c r="K64">
+      <c r="K64" s="1">
         <v>1</v>
       </c>
       <c r="L64" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>7</v>
       </c>
@@ -2639,14 +2650,14 @@
       <c r="J65" t="s">
         <v>9</v>
       </c>
-      <c r="K65">
-        <v>1</v>
+      <c r="K65" s="1">
+        <v>0</v>
       </c>
       <c r="L65" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>7</v>
       </c>
@@ -2668,14 +2679,14 @@
       <c r="J66" t="s">
         <v>9</v>
       </c>
-      <c r="K66">
-        <v>1</v>
+      <c r="K66" s="1">
+        <v>0</v>
       </c>
       <c r="L66" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>7</v>
       </c>
@@ -2703,14 +2714,14 @@
       <c r="J67" t="s">
         <v>34</v>
       </c>
-      <c r="K67">
+      <c r="K67" s="1">
         <v>1</v>
       </c>
       <c r="L67" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>7</v>
       </c>
@@ -2741,14 +2752,14 @@
       <c r="J68" t="s">
         <v>9</v>
       </c>
-      <c r="K68">
+      <c r="K68" s="1">
         <v>1</v>
       </c>
       <c r="L68" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>7</v>
       </c>
@@ -2770,14 +2781,14 @@
       <c r="J69" t="s">
         <v>9</v>
       </c>
-      <c r="K69">
-        <v>1</v>
+      <c r="K69" s="1">
+        <v>0</v>
       </c>
       <c r="L69" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>7</v>
       </c>
@@ -2799,14 +2810,14 @@
       <c r="J70" t="s">
         <v>9</v>
       </c>
-      <c r="K70">
-        <v>1</v>
+      <c r="K70" s="1">
+        <v>0</v>
       </c>
       <c r="L70" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>7</v>
       </c>
@@ -2828,14 +2839,14 @@
       <c r="J71" t="s">
         <v>9</v>
       </c>
-      <c r="K71">
-        <v>1</v>
+      <c r="K71" s="1">
+        <v>0</v>
       </c>
       <c r="L71" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>7</v>
       </c>
@@ -2848,11 +2859,11 @@
       <c r="E72">
         <v>0</v>
       </c>
-      <c r="K72">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="K72" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>7</v>
       </c>
@@ -2883,14 +2894,14 @@
       <c r="J73" t="s">
         <v>9</v>
       </c>
-      <c r="K73">
+      <c r="K73" s="1">
         <v>1</v>
       </c>
       <c r="L73" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>7</v>
       </c>
@@ -2921,14 +2932,14 @@
       <c r="J74" t="s">
         <v>9</v>
       </c>
-      <c r="K74">
+      <c r="K74" s="1">
         <v>1</v>
       </c>
       <c r="L74" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>7</v>
       </c>
@@ -2959,14 +2970,14 @@
       <c r="J75" t="s">
         <v>9</v>
       </c>
-      <c r="K75">
+      <c r="K75" s="1">
         <v>1</v>
       </c>
       <c r="L75" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>7</v>
       </c>
@@ -2997,14 +3008,14 @@
       <c r="J76" t="s">
         <v>9</v>
       </c>
-      <c r="K76">
+      <c r="K76" s="1">
         <v>1</v>
       </c>
       <c r="L76" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>7</v>
       </c>
@@ -3014,8 +3025,11 @@
       <c r="C77" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="K77" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>7</v>
       </c>
@@ -3028,11 +3042,11 @@
       <c r="E78">
         <v>0</v>
       </c>
-      <c r="K78">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="K78" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>7</v>
       </c>
@@ -3054,14 +3068,14 @@
       <c r="J79" t="s">
         <v>9</v>
       </c>
-      <c r="K79">
-        <v>1</v>
+      <c r="K79" s="1">
+        <v>0</v>
       </c>
       <c r="L79" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>7</v>
       </c>
@@ -3083,14 +3097,14 @@
       <c r="J80" t="s">
         <v>9</v>
       </c>
-      <c r="K80">
-        <v>1</v>
+      <c r="K80" s="1">
+        <v>0</v>
       </c>
       <c r="L80" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>7</v>
       </c>
@@ -3115,14 +3129,14 @@
       <c r="J81" t="s">
         <v>9</v>
       </c>
-      <c r="K81">
-        <v>1</v>
+      <c r="K81" s="1">
+        <v>0</v>
       </c>
       <c r="L81" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>7</v>
       </c>
@@ -3147,14 +3161,14 @@
       <c r="J82" t="s">
         <v>9</v>
       </c>
-      <c r="K82">
-        <v>1</v>
+      <c r="K82" s="1">
+        <v>0</v>
       </c>
       <c r="L82" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>7</v>
       </c>
@@ -3185,14 +3199,14 @@
       <c r="J83" t="s">
         <v>9</v>
       </c>
-      <c r="K83">
+      <c r="K83" s="1">
         <v>1</v>
       </c>
       <c r="L83" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>7</v>
       </c>
@@ -3220,14 +3234,14 @@
       <c r="J84" t="s">
         <v>9</v>
       </c>
-      <c r="K84">
-        <v>1</v>
+      <c r="K84" s="1">
+        <v>0</v>
       </c>
       <c r="L84" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>7</v>
       </c>
@@ -3258,14 +3272,14 @@
       <c r="J85" t="s">
         <v>9</v>
       </c>
-      <c r="K85">
-        <v>1</v>
+      <c r="K85" s="1">
+        <v>0</v>
       </c>
       <c r="L85" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>7</v>
       </c>
@@ -3287,14 +3301,14 @@
       <c r="J86" t="s">
         <v>9</v>
       </c>
-      <c r="K86">
-        <v>1</v>
+      <c r="K86" s="1">
+        <v>0</v>
       </c>
       <c r="L86" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>7</v>
       </c>
@@ -3322,14 +3336,14 @@
       <c r="J87" t="s">
         <v>9</v>
       </c>
-      <c r="K87">
-        <v>1</v>
+      <c r="K87" s="1">
+        <v>0</v>
       </c>
       <c r="L87" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>7</v>
       </c>
@@ -3351,14 +3365,14 @@
       <c r="J88" t="s">
         <v>9</v>
       </c>
-      <c r="K88">
-        <v>1</v>
+      <c r="K88" s="1">
+        <v>0</v>
       </c>
       <c r="L88" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>7</v>
       </c>
@@ -3371,11 +3385,11 @@
       <c r="E89">
         <v>0</v>
       </c>
-      <c r="K89">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="K89" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>7</v>
       </c>
@@ -3406,14 +3420,14 @@
       <c r="J90" t="s">
         <v>9</v>
       </c>
-      <c r="K90">
+      <c r="K90" s="1">
         <v>1</v>
       </c>
       <c r="L90" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>7</v>
       </c>
@@ -3444,14 +3458,14 @@
       <c r="J91" t="s">
         <v>9</v>
       </c>
-      <c r="K91">
+      <c r="K91" s="1">
         <v>1</v>
       </c>
       <c r="L91" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>7</v>
       </c>
@@ -3482,14 +3496,14 @@
       <c r="J92" t="s">
         <v>9</v>
       </c>
-      <c r="K92">
+      <c r="K92" s="1">
         <v>1</v>
       </c>
       <c r="L92" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>7</v>
       </c>
@@ -3514,14 +3528,14 @@
       <c r="J93" t="s">
         <v>9</v>
       </c>
-      <c r="K93">
-        <v>1</v>
+      <c r="K93" s="1">
+        <v>0</v>
       </c>
       <c r="L93" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>7</v>
       </c>
@@ -3543,14 +3557,14 @@
       <c r="J94" t="s">
         <v>9</v>
       </c>
-      <c r="K94">
-        <v>1</v>
+      <c r="K94" s="1">
+        <v>0</v>
       </c>
       <c r="L94" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>7</v>
       </c>
@@ -3563,11 +3577,11 @@
       <c r="E95">
         <v>0</v>
       </c>
-      <c r="K95">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="K95" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>7</v>
       </c>
@@ -3595,14 +3609,14 @@
       <c r="J96" t="s">
         <v>9</v>
       </c>
-      <c r="K96">
-        <v>1</v>
+      <c r="K96" s="1">
+        <v>0</v>
       </c>
       <c r="L96" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>7</v>
       </c>
@@ -3615,11 +3629,11 @@
       <c r="E97">
         <v>0</v>
       </c>
-      <c r="K97">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="K97" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>7</v>
       </c>
@@ -3632,11 +3646,11 @@
       <c r="E98">
         <v>0</v>
       </c>
-      <c r="K98">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="K98" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>7</v>
       </c>
@@ -3667,14 +3681,14 @@
       <c r="J99" t="s">
         <v>9</v>
       </c>
-      <c r="K99">
+      <c r="K99" s="1">
         <v>1</v>
       </c>
       <c r="L99" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>7</v>
       </c>
@@ -3702,14 +3716,14 @@
       <c r="J100" t="s">
         <v>9</v>
       </c>
-      <c r="K100">
-        <v>1</v>
+      <c r="K100" s="1">
+        <v>0</v>
       </c>
       <c r="L100" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>7</v>
       </c>
@@ -3740,14 +3754,14 @@
       <c r="J101" t="s">
         <v>9</v>
       </c>
-      <c r="K101">
+      <c r="K101" s="1">
         <v>1</v>
       </c>
       <c r="L101" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>7</v>
       </c>
@@ -3769,14 +3783,14 @@
       <c r="J102" t="s">
         <v>9</v>
       </c>
-      <c r="K102">
-        <v>1</v>
+      <c r="K102" s="1">
+        <v>0</v>
       </c>
       <c r="L102" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>7</v>
       </c>
@@ -3789,11 +3803,11 @@
       <c r="E103">
         <v>0</v>
       </c>
-      <c r="K103">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="K103" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>7</v>
       </c>
@@ -3818,14 +3832,14 @@
       <c r="J104" t="s">
         <v>9</v>
       </c>
-      <c r="K104">
-        <v>1</v>
+      <c r="K104" s="1">
+        <v>0</v>
       </c>
       <c r="L104" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>7</v>
       </c>
@@ -3856,14 +3870,14 @@
       <c r="J105" t="s">
         <v>9</v>
       </c>
-      <c r="K105">
+      <c r="K105" s="1">
         <v>1</v>
       </c>
       <c r="L105" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>7</v>
       </c>
@@ -3891,14 +3905,14 @@
       <c r="J106" t="s">
         <v>9</v>
       </c>
-      <c r="K106">
-        <v>1</v>
+      <c r="K106" s="1">
+        <v>0</v>
       </c>
       <c r="L106" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>7</v>
       </c>
@@ -3929,14 +3943,14 @@
       <c r="J107" t="s">
         <v>9</v>
       </c>
-      <c r="K107">
+      <c r="K107" s="1">
         <v>1</v>
       </c>
       <c r="L107" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>7</v>
       </c>
@@ -3967,14 +3981,14 @@
       <c r="J108" t="s">
         <v>9</v>
       </c>
-      <c r="K108">
+      <c r="K108" s="1">
         <v>1</v>
       </c>
       <c r="L108" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>7</v>
       </c>
@@ -4002,14 +4016,14 @@
       <c r="J109" t="s">
         <v>9</v>
       </c>
-      <c r="K109">
+      <c r="K109" s="1">
         <v>1</v>
       </c>
       <c r="L109" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>7</v>
       </c>
@@ -4040,7 +4054,7 @@
       <c r="J110" t="s">
         <v>9</v>
       </c>
-      <c r="K110">
+      <c r="K110" s="1">
         <v>1</v>
       </c>
       <c r="L110" t="s">
@@ -4050,7 +4064,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>7</v>
       </c>
@@ -4075,11 +4089,14 @@
       <c r="J111" t="s">
         <v>9</v>
       </c>
+      <c r="K111" s="1">
+        <v>1</v>
+      </c>
       <c r="L111" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>7</v>
       </c>
@@ -4110,14 +4127,14 @@
       <c r="J112" t="s">
         <v>9</v>
       </c>
-      <c r="K112">
-        <v>1</v>
+      <c r="K112" s="1">
+        <v>0</v>
       </c>
       <c r="L112" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>7</v>
       </c>
@@ -4142,14 +4159,14 @@
       <c r="J113" t="s">
         <v>9</v>
       </c>
-      <c r="K113">
-        <v>1</v>
+      <c r="K113" s="1">
+        <v>0</v>
       </c>
       <c r="L113" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>7</v>
       </c>
@@ -4162,11 +4179,11 @@
       <c r="E114">
         <v>0</v>
       </c>
-      <c r="K114">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="K114" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>7</v>
       </c>
@@ -4179,11 +4196,11 @@
       <c r="E115">
         <v>0</v>
       </c>
-      <c r="K115">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="K115" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>7</v>
       </c>
@@ -4205,14 +4222,14 @@
       <c r="J116" t="s">
         <v>33</v>
       </c>
-      <c r="K116">
-        <v>1</v>
+      <c r="K116" s="1">
+        <v>0</v>
       </c>
       <c r="L116" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>7</v>
       </c>
@@ -4237,14 +4254,14 @@
       <c r="J117" t="s">
         <v>9</v>
       </c>
-      <c r="K117">
-        <v>1</v>
+      <c r="K117" s="1">
+        <v>0</v>
       </c>
       <c r="L117" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>7</v>
       </c>
@@ -4275,14 +4292,14 @@
       <c r="J118" t="s">
         <v>9</v>
       </c>
-      <c r="K118">
+      <c r="K118" s="1">
         <v>1</v>
       </c>
       <c r="L118" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>7</v>
       </c>
@@ -4313,14 +4330,14 @@
       <c r="J119" t="s">
         <v>9</v>
       </c>
-      <c r="K119">
-        <v>1</v>
+      <c r="K119" s="1">
+        <v>0</v>
       </c>
       <c r="L119" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>7</v>
       </c>
@@ -4333,11 +4350,11 @@
       <c r="E120">
         <v>0</v>
       </c>
-      <c r="K120">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="K120" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>7</v>
       </c>
@@ -4359,14 +4376,14 @@
       <c r="J121" t="s">
         <v>9</v>
       </c>
-      <c r="K121">
-        <v>1</v>
+      <c r="K121" s="1">
+        <v>0</v>
       </c>
       <c r="L121" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>7</v>
       </c>
@@ -4397,14 +4414,14 @@
       <c r="J122" t="s">
         <v>9</v>
       </c>
-      <c r="K122">
+      <c r="K122" s="1">
         <v>1</v>
       </c>
       <c r="L122" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>7</v>
       </c>
@@ -4417,11 +4434,11 @@
       <c r="E123">
         <v>0</v>
       </c>
-      <c r="K123">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="K123" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>7</v>
       </c>
@@ -4452,14 +4469,14 @@
       <c r="J124" t="s">
         <v>9</v>
       </c>
-      <c r="K124">
+      <c r="K124" s="1">
         <v>1</v>
       </c>
       <c r="L124" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>7</v>
       </c>
@@ -4490,14 +4507,14 @@
       <c r="J125" t="s">
         <v>9</v>
       </c>
-      <c r="K125">
-        <v>1</v>
+      <c r="K125" s="1">
+        <v>0</v>
       </c>
       <c r="L125" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>7</v>
       </c>
@@ -4528,14 +4545,14 @@
       <c r="J126" t="s">
         <v>9</v>
       </c>
-      <c r="K126">
-        <v>1</v>
+      <c r="K126" s="1">
+        <v>0</v>
       </c>
       <c r="L126" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>7</v>
       </c>
@@ -4566,14 +4583,14 @@
       <c r="J127" t="s">
         <v>9</v>
       </c>
-      <c r="K127">
+      <c r="K127" s="1">
         <v>1</v>
       </c>
       <c r="L127" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>7</v>
       </c>
@@ -4604,14 +4621,14 @@
       <c r="J128" t="s">
         <v>9</v>
       </c>
-      <c r="K128">
+      <c r="K128" s="1">
         <v>1</v>
       </c>
       <c r="L128" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>7</v>
       </c>
@@ -4642,14 +4659,14 @@
       <c r="J129" t="s">
         <v>9</v>
       </c>
-      <c r="K129">
+      <c r="K129" s="1">
         <v>1</v>
       </c>
       <c r="L129" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>7</v>
       </c>
@@ -4680,14 +4697,14 @@
       <c r="J130" t="s">
         <v>9</v>
       </c>
-      <c r="K130">
+      <c r="K130" s="1">
         <v>1</v>
       </c>
       <c r="L130" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>7</v>
       </c>
@@ -4709,14 +4726,14 @@
       <c r="J131" t="s">
         <v>9</v>
       </c>
-      <c r="K131">
-        <v>1</v>
+      <c r="K131" s="1">
+        <v>0</v>
       </c>
       <c r="L131" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>7</v>
       </c>
@@ -4741,14 +4758,14 @@
       <c r="J132" t="s">
         <v>9</v>
       </c>
-      <c r="K132">
-        <v>1</v>
+      <c r="K132" s="1">
+        <v>0</v>
       </c>
       <c r="L132" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>7</v>
       </c>
@@ -4770,14 +4787,14 @@
       <c r="J133" t="s">
         <v>9</v>
       </c>
-      <c r="K133">
-        <v>1</v>
+      <c r="K133" s="1">
+        <v>0</v>
       </c>
       <c r="L133" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>7</v>
       </c>
@@ -4799,14 +4816,14 @@
       <c r="J134" t="s">
         <v>9</v>
       </c>
-      <c r="K134">
+      <c r="K134" s="1">
         <v>1</v>
       </c>
       <c r="L134" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>7</v>
       </c>
@@ -4828,14 +4845,14 @@
       <c r="J135" t="s">
         <v>9</v>
       </c>
-      <c r="K135">
-        <v>1</v>
+      <c r="K135" s="1">
+        <v>0</v>
       </c>
       <c r="L135" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>7</v>
       </c>
@@ -4848,11 +4865,11 @@
       <c r="E136">
         <v>0</v>
       </c>
-      <c r="K136">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="K136" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>7</v>
       </c>
@@ -4865,11 +4882,11 @@
       <c r="E137">
         <v>0</v>
       </c>
-      <c r="K137">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="K137" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>7</v>
       </c>
@@ -4900,14 +4917,14 @@
       <c r="J138" t="s">
         <v>9</v>
       </c>
-      <c r="K138">
+      <c r="K138" s="1">
         <v>1</v>
       </c>
       <c r="L138" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>7</v>
       </c>
@@ -4935,14 +4952,14 @@
       <c r="J139" t="s">
         <v>9</v>
       </c>
-      <c r="K139">
-        <v>1</v>
+      <c r="K139" s="1">
+        <v>0</v>
       </c>
       <c r="L139" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>7</v>
       </c>
@@ -4973,14 +4990,14 @@
       <c r="J140" t="s">
         <v>9</v>
       </c>
-      <c r="K140">
+      <c r="K140" s="1">
         <v>1</v>
       </c>
       <c r="L140" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>7</v>
       </c>
@@ -5011,14 +5028,14 @@
       <c r="J141" t="s">
         <v>9</v>
       </c>
-      <c r="K141">
+      <c r="K141" s="1">
         <v>1</v>
       </c>
       <c r="L141" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>7</v>
       </c>
@@ -5040,11 +5057,11 @@
       <c r="J142" t="s">
         <v>9</v>
       </c>
-      <c r="K142">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="K142" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>7</v>
       </c>
@@ -5069,14 +5086,14 @@
       <c r="J143" t="s">
         <v>9</v>
       </c>
-      <c r="K143">
-        <v>1</v>
+      <c r="K143" s="1">
+        <v>0</v>
       </c>
       <c r="L143" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>7</v>
       </c>
@@ -5098,14 +5115,14 @@
       <c r="J144" t="s">
         <v>9</v>
       </c>
-      <c r="K144">
-        <v>1</v>
+      <c r="K144" s="1">
+        <v>0</v>
       </c>
       <c r="L144" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>7</v>
       </c>
@@ -5136,14 +5153,14 @@
       <c r="J145" t="s">
         <v>9</v>
       </c>
-      <c r="K145">
+      <c r="K145" s="1">
         <v>1</v>
       </c>
       <c r="L145" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>7</v>
       </c>
@@ -5174,14 +5191,14 @@
       <c r="J146" t="s">
         <v>9</v>
       </c>
-      <c r="K146">
+      <c r="K146" s="1">
         <v>1</v>
       </c>
       <c r="L146" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>7</v>
       </c>
@@ -5203,14 +5220,14 @@
       <c r="J147" t="s">
         <v>9</v>
       </c>
-      <c r="K147">
-        <v>1</v>
+      <c r="K147" s="1">
+        <v>0</v>
       </c>
       <c r="L147" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>7</v>
       </c>
@@ -5241,14 +5258,14 @@
       <c r="J148" t="s">
         <v>9</v>
       </c>
-      <c r="K148">
+      <c r="K148" s="1">
         <v>1</v>
       </c>
       <c r="L148" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>7</v>
       </c>
@@ -5279,14 +5296,14 @@
       <c r="J149" t="s">
         <v>9</v>
       </c>
-      <c r="K149">
+      <c r="K149" s="1">
         <v>1</v>
       </c>
       <c r="L149" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>7</v>
       </c>
@@ -5317,14 +5334,14 @@
       <c r="J150" t="s">
         <v>9</v>
       </c>
-      <c r="K150">
+      <c r="K150" s="1">
         <v>1</v>
       </c>
       <c r="L150" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>7</v>
       </c>
@@ -5352,14 +5369,14 @@
       <c r="J151" t="s">
         <v>9</v>
       </c>
-      <c r="K151">
-        <v>1</v>
+      <c r="K151" s="1">
+        <v>0</v>
       </c>
       <c r="L151" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>7</v>
       </c>
@@ -5390,14 +5407,14 @@
       <c r="J152" t="s">
         <v>9</v>
       </c>
-      <c r="K152">
+      <c r="K152" s="1">
         <v>1</v>
       </c>
       <c r="L152" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>7</v>
       </c>
@@ -5428,14 +5445,14 @@
       <c r="J153" t="s">
         <v>9</v>
       </c>
-      <c r="K153">
+      <c r="K153" s="1">
         <v>1</v>
       </c>
       <c r="L153" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>7</v>
       </c>
@@ -5466,14 +5483,14 @@
       <c r="J154" t="s">
         <v>9</v>
       </c>
-      <c r="K154">
+      <c r="K154" s="1">
         <v>1</v>
       </c>
       <c r="L154" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>7</v>
       </c>
@@ -5504,14 +5521,14 @@
       <c r="J155" t="s">
         <v>33</v>
       </c>
-      <c r="K155">
+      <c r="K155" s="1">
         <v>1</v>
       </c>
       <c r="L155" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>7</v>
       </c>
@@ -5542,14 +5559,14 @@
       <c r="J156" t="s">
         <v>33</v>
       </c>
-      <c r="K156">
+      <c r="K156" s="1">
         <v>1</v>
       </c>
       <c r="L156" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>7</v>
       </c>
@@ -5571,14 +5588,14 @@
       <c r="J157" t="s">
         <v>9</v>
       </c>
-      <c r="K157">
-        <v>1</v>
+      <c r="K157" s="1">
+        <v>0</v>
       </c>
       <c r="L157" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>7</v>
       </c>
@@ -5603,14 +5620,14 @@
       <c r="J158" t="s">
         <v>9</v>
       </c>
-      <c r="K158">
-        <v>1</v>
+      <c r="K158" s="1">
+        <v>0</v>
       </c>
       <c r="L158" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>7</v>
       </c>
@@ -5632,14 +5649,14 @@
       <c r="J159" t="s">
         <v>9</v>
       </c>
-      <c r="K159">
-        <v>1</v>
+      <c r="K159" s="1">
+        <v>0</v>
       </c>
       <c r="L159" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>7</v>
       </c>
@@ -5670,14 +5687,14 @@
       <c r="J160" t="s">
         <v>9</v>
       </c>
-      <c r="K160">
+      <c r="K160" s="1">
         <v>1</v>
       </c>
       <c r="L160" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>7</v>
       </c>
@@ -5708,14 +5725,14 @@
       <c r="J161" t="s">
         <v>9</v>
       </c>
-      <c r="K161">
+      <c r="K161" s="1">
         <v>1</v>
       </c>
       <c r="L161" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>7</v>
       </c>
@@ -5737,14 +5754,14 @@
       <c r="J162" t="s">
         <v>9</v>
       </c>
-      <c r="K162">
-        <v>1</v>
+      <c r="K162" s="1">
+        <v>0</v>
       </c>
       <c r="L162" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>7</v>
       </c>
@@ -5769,14 +5786,14 @@
       <c r="J163" t="s">
         <v>9</v>
       </c>
-      <c r="K163">
+      <c r="K163" s="1">
         <v>1</v>
       </c>
       <c r="L163" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>7</v>
       </c>
@@ -5789,11 +5806,11 @@
       <c r="E164">
         <v>0</v>
       </c>
-      <c r="K164">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="K164" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>7</v>
       </c>
@@ -5806,11 +5823,11 @@
       <c r="E165">
         <v>0</v>
       </c>
-      <c r="K165">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="K165" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>7</v>
       </c>
@@ -5841,14 +5858,14 @@
       <c r="J166" t="s">
         <v>9</v>
       </c>
-      <c r="K166">
+      <c r="K166" s="1">
         <v>1</v>
       </c>
       <c r="L166" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>7</v>
       </c>
@@ -5870,14 +5887,14 @@
       <c r="J167" t="s">
         <v>9</v>
       </c>
-      <c r="K167">
-        <v>1</v>
+      <c r="K167" s="1">
+        <v>0</v>
       </c>
       <c r="L167" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>7</v>
       </c>
@@ -5899,14 +5916,14 @@
       <c r="J168" t="s">
         <v>9</v>
       </c>
-      <c r="K168">
-        <v>1</v>
+      <c r="K168" s="1">
+        <v>0</v>
       </c>
       <c r="L168" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>7</v>
       </c>
@@ -5934,14 +5951,14 @@
       <c r="J169" t="s">
         <v>9</v>
       </c>
-      <c r="K169">
+      <c r="K169" s="1">
         <v>1</v>
       </c>
       <c r="L169" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>7</v>
       </c>
@@ -5960,14 +5977,14 @@
       <c r="J170" t="s">
         <v>9</v>
       </c>
-      <c r="K170">
-        <v>1</v>
+      <c r="K170" s="1">
+        <v>0</v>
       </c>
       <c r="L170" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>7</v>
       </c>
@@ -5989,14 +6006,14 @@
       <c r="J171" t="s">
         <v>9</v>
       </c>
-      <c r="K171">
+      <c r="K171" s="1">
         <v>1</v>
       </c>
       <c r="L171" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>7</v>
       </c>
@@ -6021,14 +6038,14 @@
       <c r="J172" t="s">
         <v>9</v>
       </c>
-      <c r="K172">
+      <c r="K172" s="1">
         <v>1</v>
       </c>
       <c r="L172" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>7</v>
       </c>
@@ -6050,14 +6067,14 @@
       <c r="J173" t="s">
         <v>9</v>
       </c>
-      <c r="K173">
-        <v>1</v>
+      <c r="K173" s="1">
+        <v>0</v>
       </c>
       <c r="L173" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>7</v>
       </c>
@@ -6085,14 +6102,14 @@
       <c r="J174" t="s">
         <v>9</v>
       </c>
-      <c r="K174">
+      <c r="K174" s="1">
         <v>1</v>
       </c>
       <c r="L174" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>7</v>
       </c>
@@ -6120,14 +6137,14 @@
       <c r="J175" t="s">
         <v>9</v>
       </c>
-      <c r="K175">
+      <c r="K175" s="1">
         <v>1</v>
       </c>
       <c r="L175" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>7</v>
       </c>
@@ -6155,14 +6172,14 @@
       <c r="J176" t="s">
         <v>9</v>
       </c>
-      <c r="K176">
+      <c r="K176" s="1">
         <v>1</v>
       </c>
       <c r="L176" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>7</v>
       </c>
@@ -6184,14 +6201,14 @@
       <c r="J177" t="s">
         <v>9</v>
       </c>
-      <c r="K177">
+      <c r="K177" s="1">
         <v>1</v>
       </c>
       <c r="L177" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="178" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>7</v>
       </c>
@@ -6207,11 +6224,11 @@
       <c r="J178">
         <v>0</v>
       </c>
-      <c r="K178">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="K178" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>7</v>
       </c>
@@ -6227,11 +6244,11 @@
       <c r="J179">
         <v>0</v>
       </c>
-      <c r="K179">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="180" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="K179" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>7</v>
       </c>
@@ -6247,11 +6264,11 @@
       <c r="J180">
         <v>0</v>
       </c>
-      <c r="K180">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="181" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="K180" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>7</v>
       </c>
@@ -6279,14 +6296,14 @@
       <c r="J181" t="s">
         <v>9</v>
       </c>
-      <c r="K181">
+      <c r="K181" s="1">
         <v>1</v>
       </c>
       <c r="L181" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>7</v>
       </c>
@@ -6311,14 +6328,14 @@
       <c r="J182" t="s">
         <v>34</v>
       </c>
-      <c r="K182">
-        <v>1</v>
+      <c r="K182" s="1">
+        <v>0</v>
       </c>
       <c r="L182" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>7</v>
       </c>
@@ -6340,14 +6357,14 @@
       <c r="J183" t="s">
         <v>9</v>
       </c>
-      <c r="K183">
-        <v>1</v>
+      <c r="K183" s="1">
+        <v>0</v>
       </c>
       <c r="L183" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="184" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>7</v>
       </c>
@@ -6372,14 +6389,14 @@
       <c r="J184" t="s">
         <v>9</v>
       </c>
-      <c r="K184">
-        <v>1</v>
+      <c r="K184" s="1">
+        <v>0</v>
       </c>
       <c r="L184" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="185" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>7</v>
       </c>
@@ -6407,14 +6424,14 @@
       <c r="J185" t="s">
         <v>9</v>
       </c>
-      <c r="K185">
+      <c r="K185" s="1">
         <v>1</v>
       </c>
       <c r="L185" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="186" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>7</v>
       </c>
@@ -6439,14 +6456,14 @@
       <c r="J186" t="s">
         <v>9</v>
       </c>
-      <c r="K186">
-        <v>1</v>
+      <c r="K186" s="1">
+        <v>0</v>
       </c>
       <c r="L186" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="187" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>7</v>
       </c>
@@ -6474,14 +6491,14 @@
       <c r="J187" t="s">
         <v>9</v>
       </c>
-      <c r="K187">
+      <c r="K187" s="1">
         <v>1</v>
       </c>
       <c r="L187" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="188" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>7</v>
       </c>
@@ -6509,14 +6526,14 @@
       <c r="J188" t="s">
         <v>9</v>
       </c>
-      <c r="K188">
+      <c r="K188" s="1">
         <v>1</v>
       </c>
       <c r="L188" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="189" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>7</v>
       </c>
@@ -6544,14 +6561,14 @@
       <c r="J189" t="s">
         <v>9</v>
       </c>
-      <c r="K189">
-        <v>1</v>
+      <c r="K189" s="1">
+        <v>0</v>
       </c>
       <c r="L189" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="190" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>7</v>
       </c>
@@ -6576,14 +6593,14 @@
       <c r="J190" t="s">
         <v>9</v>
       </c>
-      <c r="K190">
-        <v>1</v>
+      <c r="K190" s="1">
+        <v>0</v>
       </c>
       <c r="L190" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="191" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>7</v>
       </c>
@@ -6611,14 +6628,14 @@
       <c r="J191" t="s">
         <v>9</v>
       </c>
-      <c r="K191">
+      <c r="K191" s="1">
         <v>1</v>
       </c>
       <c r="L191" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="192" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>7</v>
       </c>
@@ -6646,14 +6663,14 @@
       <c r="J192" t="s">
         <v>9</v>
       </c>
-      <c r="K192">
+      <c r="K192" s="1">
         <v>1</v>
       </c>
       <c r="L192" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="193" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>7</v>
       </c>
@@ -6675,14 +6692,14 @@
       <c r="J193" t="s">
         <v>9</v>
       </c>
-      <c r="K193">
-        <v>1</v>
+      <c r="K193" s="1">
+        <v>0</v>
       </c>
       <c r="L193" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="194" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>7</v>
       </c>
@@ -6707,14 +6724,14 @@
       <c r="J194" t="s">
         <v>9</v>
       </c>
-      <c r="K194">
+      <c r="K194" s="1">
         <v>1</v>
       </c>
       <c r="L194" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="195" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>7</v>
       </c>
@@ -6742,14 +6759,14 @@
       <c r="J195" t="s">
         <v>9</v>
       </c>
-      <c r="K195">
+      <c r="K195" s="1">
         <v>1</v>
       </c>
       <c r="L195" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="196" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>7</v>
       </c>
@@ -6765,11 +6782,11 @@
       <c r="J196">
         <v>0</v>
       </c>
-      <c r="K196">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="197" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="K196" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>7</v>
       </c>
@@ -6794,14 +6811,14 @@
       <c r="J197" t="s">
         <v>9</v>
       </c>
-      <c r="K197">
-        <v>1</v>
+      <c r="K197" s="1">
+        <v>0</v>
       </c>
       <c r="L197" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="198" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>7</v>
       </c>
@@ -6829,14 +6846,14 @@
       <c r="J198" t="s">
         <v>9</v>
       </c>
-      <c r="K198">
+      <c r="K198" s="1">
         <v>1</v>
       </c>
       <c r="L198" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="199" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>7</v>
       </c>
@@ -6858,14 +6875,14 @@
       <c r="J199" t="s">
         <v>9</v>
       </c>
-      <c r="K199">
+      <c r="K199" s="1">
         <v>1</v>
       </c>
       <c r="L199" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="200" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>7</v>
       </c>
@@ -6887,14 +6904,14 @@
       <c r="J200" t="s">
         <v>9</v>
       </c>
-      <c r="K200">
+      <c r="K200" s="1">
         <v>1</v>
       </c>
       <c r="L200" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="201" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>7</v>
       </c>
@@ -6910,11 +6927,11 @@
       <c r="J201">
         <v>0</v>
       </c>
-      <c r="K201">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="202" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="K201" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>7</v>
       </c>
@@ -6942,14 +6959,14 @@
       <c r="J202" t="s">
         <v>9</v>
       </c>
-      <c r="K202">
+      <c r="K202" s="1">
         <v>1</v>
       </c>
       <c r="L202" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="203" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>7</v>
       </c>
@@ -6971,14 +6988,14 @@
       <c r="J203" t="s">
         <v>9</v>
       </c>
-      <c r="K203">
-        <v>1</v>
+      <c r="K203" s="1">
+        <v>0</v>
       </c>
       <c r="L203" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="204" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>7</v>
       </c>
@@ -7006,14 +7023,14 @@
       <c r="J204" t="s">
         <v>9</v>
       </c>
-      <c r="K204">
+      <c r="K204" s="1">
         <v>1</v>
       </c>
       <c r="L204" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="205" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>7</v>
       </c>
@@ -7032,14 +7049,14 @@
       <c r="J205" t="s">
         <v>72</v>
       </c>
-      <c r="K205">
+      <c r="K205" s="1">
         <v>1</v>
       </c>
       <c r="L205" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="206" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>7</v>
       </c>
@@ -7058,14 +7075,14 @@
       <c r="J206" t="s">
         <v>9</v>
       </c>
-      <c r="K206">
+      <c r="K206" s="1">
         <v>1</v>
       </c>
       <c r="L206" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="207" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>7</v>
       </c>
@@ -7084,14 +7101,14 @@
       <c r="J207" t="s">
         <v>72</v>
       </c>
-      <c r="K207">
+      <c r="K207" s="1">
         <v>1</v>
       </c>
       <c r="L207" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="208" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>7</v>
       </c>
@@ -7110,14 +7127,14 @@
       <c r="J208" t="s">
         <v>72</v>
       </c>
-      <c r="K208">
+      <c r="K208" s="1">
         <v>1</v>
       </c>
       <c r="L208" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="209" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
         <v>7</v>
       </c>
@@ -7136,14 +7153,14 @@
       <c r="J209" t="s">
         <v>9</v>
       </c>
-      <c r="K209">
+      <c r="K209" s="1">
         <v>1</v>
       </c>
       <c r="L209" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="210" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
         <v>7</v>
       </c>
@@ -7162,14 +7179,14 @@
       <c r="J210" t="s">
         <v>9</v>
       </c>
-      <c r="K210">
+      <c r="K210" s="1">
         <v>1</v>
       </c>
       <c r="L210" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="211" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>7</v>
       </c>
@@ -7188,14 +7205,14 @@
       <c r="J211" t="s">
         <v>9</v>
       </c>
-      <c r="K211">
+      <c r="K211" s="1">
         <v>1</v>
       </c>
       <c r="L211" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="212" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
         <v>7</v>
       </c>
@@ -7214,14 +7231,14 @@
       <c r="J212" t="s">
         <v>9</v>
       </c>
-      <c r="K212">
+      <c r="K212" s="1">
         <v>1</v>
       </c>
       <c r="L212" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="213" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
         <v>7</v>
       </c>
@@ -7240,14 +7257,14 @@
       <c r="J213" t="s">
         <v>72</v>
       </c>
-      <c r="K213">
+      <c r="K213" s="1">
         <v>1</v>
       </c>
       <c r="L213" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="214" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
         <v>7</v>
       </c>
@@ -7266,14 +7283,14 @@
       <c r="J214" t="s">
         <v>9</v>
       </c>
-      <c r="K214">
+      <c r="K214" s="1">
         <v>1</v>
       </c>
       <c r="L214" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="215" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>7</v>
       </c>
@@ -7292,14 +7309,14 @@
       <c r="J215" t="s">
         <v>9</v>
       </c>
-      <c r="K215">
+      <c r="K215" s="1">
         <v>1</v>
       </c>
       <c r="L215" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="216" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
         <v>7</v>
       </c>
@@ -7318,14 +7335,14 @@
       <c r="J216" t="s">
         <v>9</v>
       </c>
-      <c r="K216">
+      <c r="K216" s="1">
         <v>1</v>
       </c>
       <c r="L216" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="217" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
         <v>7</v>
       </c>
@@ -7344,14 +7361,14 @@
       <c r="J217" t="s">
         <v>72</v>
       </c>
-      <c r="K217">
+      <c r="K217" s="1">
         <v>1</v>
       </c>
       <c r="L217" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="218" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
         <v>7</v>
       </c>
@@ -7370,14 +7387,14 @@
       <c r="J218" t="s">
         <v>9</v>
       </c>
-      <c r="K218">
+      <c r="K218" s="1">
         <v>1</v>
       </c>
       <c r="L218" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="219" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
         <v>7</v>
       </c>
@@ -7396,14 +7413,14 @@
       <c r="J219" t="s">
         <v>9</v>
       </c>
-      <c r="K219">
+      <c r="K219" s="1">
         <v>1</v>
       </c>
       <c r="L219" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="220" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>7</v>
       </c>
@@ -7422,14 +7439,14 @@
       <c r="J220" t="s">
         <v>9</v>
       </c>
-      <c r="K220">
+      <c r="K220" s="1">
         <v>1</v>
       </c>
       <c r="L220" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="221" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
         <v>7</v>
       </c>
@@ -7448,14 +7465,14 @@
       <c r="J221" t="s">
         <v>9</v>
       </c>
-      <c r="K221">
+      <c r="K221" s="1">
         <v>1</v>
       </c>
       <c r="L221" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="222" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>7</v>
       </c>
@@ -7474,14 +7491,14 @@
       <c r="J222" t="s">
         <v>9</v>
       </c>
-      <c r="K222">
+      <c r="K222" s="1">
         <v>1</v>
       </c>
       <c r="L222" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="223" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>7</v>
       </c>
@@ -7500,14 +7517,14 @@
       <c r="J223" t="s">
         <v>9</v>
       </c>
-      <c r="K223">
+      <c r="K223" s="1">
         <v>1</v>
       </c>
       <c r="L223" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="224" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
         <v>7</v>
       </c>
@@ -7526,14 +7543,14 @@
       <c r="J224" t="s">
         <v>9</v>
       </c>
-      <c r="K224">
+      <c r="K224" s="1">
         <v>1</v>
       </c>
       <c r="L224" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="225" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>7</v>
       </c>
@@ -7552,7 +7569,7 @@
       <c r="J225" t="s">
         <v>9</v>
       </c>
-      <c r="K225">
+      <c r="K225" s="1">
         <v>1</v>
       </c>
       <c r="L225" t="s">
@@ -7562,7 +7579,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="226" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
         <v>7</v>
       </c>
@@ -7581,14 +7598,14 @@
       <c r="J226" t="s">
         <v>9</v>
       </c>
-      <c r="K226">
+      <c r="K226" s="1">
         <v>1</v>
       </c>
       <c r="L226" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="227" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
         <v>7</v>
       </c>
@@ -7607,14 +7624,14 @@
       <c r="J227" t="s">
         <v>9</v>
       </c>
-      <c r="K227">
+      <c r="K227" s="1">
         <v>1</v>
       </c>
       <c r="L227" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="228" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
         <v>7</v>
       </c>
@@ -7633,14 +7650,14 @@
       <c r="J228" t="s">
         <v>9</v>
       </c>
-      <c r="K228">
+      <c r="K228" s="1">
         <v>1</v>
       </c>
       <c r="L228" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="229" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
         <v>7</v>
       </c>
@@ -7659,14 +7676,14 @@
       <c r="J229" t="s">
         <v>9</v>
       </c>
-      <c r="K229">
+      <c r="K229" s="1">
         <v>1</v>
       </c>
       <c r="L229" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="230" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
         <v>7</v>
       </c>
@@ -7685,14 +7702,14 @@
       <c r="J230" t="s">
         <v>9</v>
       </c>
-      <c r="K230">
+      <c r="K230" s="1">
         <v>1</v>
       </c>
       <c r="L230" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="231" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
         <v>7</v>
       </c>
@@ -7711,14 +7728,14 @@
       <c r="J231" t="s">
         <v>9</v>
       </c>
-      <c r="K231">
+      <c r="K231" s="1">
         <v>1</v>
       </c>
       <c r="L231" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="232" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
         <v>7</v>
       </c>
@@ -7737,14 +7754,14 @@
       <c r="J232" t="s">
         <v>9</v>
       </c>
-      <c r="K232">
+      <c r="K232" s="1">
         <v>1</v>
       </c>
       <c r="L232" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="233" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
         <v>7</v>
       </c>
@@ -7763,14 +7780,14 @@
       <c r="J233" t="s">
         <v>9</v>
       </c>
-      <c r="K233">
+      <c r="K233" s="1">
         <v>1</v>
       </c>
       <c r="L233" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="234" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
         <v>7</v>
       </c>
@@ -7789,14 +7806,14 @@
       <c r="J234" t="s">
         <v>9</v>
       </c>
-      <c r="K234">
+      <c r="K234" s="1">
         <v>1</v>
       </c>
       <c r="L234" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="235" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
         <v>7</v>
       </c>
@@ -7815,14 +7832,14 @@
       <c r="J235" t="s">
         <v>9</v>
       </c>
-      <c r="K235">
+      <c r="K235" s="1">
         <v>1</v>
       </c>
       <c r="L235" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="236" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
         <v>7</v>
       </c>
@@ -7841,14 +7858,14 @@
       <c r="J236" t="s">
         <v>9</v>
       </c>
-      <c r="K236">
+      <c r="K236" s="1">
         <v>1</v>
       </c>
       <c r="L236" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="237" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
         <v>7</v>
       </c>
@@ -7867,14 +7884,14 @@
       <c r="J237" t="s">
         <v>9</v>
       </c>
-      <c r="K237">
+      <c r="K237" s="1">
         <v>1</v>
       </c>
       <c r="L237" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="238" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
         <v>7</v>
       </c>
@@ -7893,14 +7910,14 @@
       <c r="J238" t="s">
         <v>9</v>
       </c>
-      <c r="K238">
+      <c r="K238" s="1">
         <v>1</v>
       </c>
       <c r="L238" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="239" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
         <v>7</v>
       </c>
@@ -7919,14 +7936,14 @@
       <c r="J239" t="s">
         <v>9</v>
       </c>
-      <c r="K239">
+      <c r="K239" s="1">
         <v>1</v>
       </c>
       <c r="L239" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="240" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
         <v>7</v>
       </c>
@@ -7945,14 +7962,14 @@
       <c r="J240" t="s">
         <v>9</v>
       </c>
-      <c r="K240">
+      <c r="K240" s="1">
         <v>1</v>
       </c>
       <c r="L240" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="241" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
         <v>7</v>
       </c>
@@ -7971,14 +7988,14 @@
       <c r="J241" t="s">
         <v>9</v>
       </c>
-      <c r="K241">
+      <c r="K241" s="1">
         <v>1</v>
       </c>
       <c r="L241" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="242" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
         <v>7</v>
       </c>
@@ -7997,14 +8014,14 @@
       <c r="J242" t="s">
         <v>9</v>
       </c>
-      <c r="K242">
+      <c r="K242" s="1">
         <v>1</v>
       </c>
       <c r="L242" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="243" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
         <v>7</v>
       </c>
@@ -8023,14 +8040,14 @@
       <c r="J243" t="s">
         <v>9</v>
       </c>
-      <c r="K243">
+      <c r="K243" s="1">
         <v>1</v>
       </c>
       <c r="L243" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="244" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
         <v>7</v>
       </c>
@@ -8049,14 +8066,14 @@
       <c r="J244" t="s">
         <v>9</v>
       </c>
-      <c r="K244">
+      <c r="K244" s="1">
         <v>1</v>
       </c>
       <c r="L244" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="245" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
         <v>7</v>
       </c>
@@ -8075,14 +8092,14 @@
       <c r="J245" t="s">
         <v>9</v>
       </c>
-      <c r="K245">
+      <c r="K245" s="1">
         <v>1</v>
       </c>
       <c r="L245" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="246" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
         <v>7</v>
       </c>
@@ -8101,14 +8118,14 @@
       <c r="J246" t="s">
         <v>9</v>
       </c>
-      <c r="K246">
+      <c r="K246" s="1">
         <v>1</v>
       </c>
       <c r="L246" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="247" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
         <v>7</v>
       </c>
@@ -8127,14 +8144,14 @@
       <c r="J247" t="s">
         <v>9</v>
       </c>
-      <c r="K247">
+      <c r="K247" s="1">
         <v>1</v>
       </c>
       <c r="L247" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="248" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
         <v>7</v>
       </c>
@@ -8153,14 +8170,14 @@
       <c r="J248" t="s">
         <v>9</v>
       </c>
-      <c r="K248">
+      <c r="K248" s="1">
         <v>1</v>
       </c>
       <c r="L248" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="249" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
         <v>7</v>
       </c>
@@ -8179,14 +8196,14 @@
       <c r="J249" t="s">
         <v>9</v>
       </c>
-      <c r="K249">
+      <c r="K249" s="1">
         <v>1</v>
       </c>
       <c r="L249" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="250" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
         <v>7</v>
       </c>
@@ -8205,14 +8222,14 @@
       <c r="J250" t="s">
         <v>9</v>
       </c>
-      <c r="K250">
+      <c r="K250" s="1">
         <v>1</v>
       </c>
       <c r="L250" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="251" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
         <v>7</v>
       </c>
@@ -8231,14 +8248,14 @@
       <c r="J251" t="s">
         <v>9</v>
       </c>
-      <c r="K251">
+      <c r="K251" s="1">
         <v>1</v>
       </c>
       <c r="L251" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="252" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
         <v>7</v>
       </c>
@@ -8257,14 +8274,14 @@
       <c r="J252" t="s">
         <v>9</v>
       </c>
-      <c r="K252">
+      <c r="K252" s="1">
         <v>1</v>
       </c>
       <c r="L252" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="253" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
         <v>7</v>
       </c>
@@ -8283,14 +8300,14 @@
       <c r="J253" t="s">
         <v>9</v>
       </c>
-      <c r="K253">
+      <c r="K253" s="1">
         <v>1</v>
       </c>
       <c r="L253" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="254" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
         <v>7</v>
       </c>
@@ -8309,14 +8326,14 @@
       <c r="J254" t="s">
         <v>9</v>
       </c>
-      <c r="K254">
+      <c r="K254" s="1">
         <v>1</v>
       </c>
       <c r="L254" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="255" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
         <v>7</v>
       </c>
@@ -8335,14 +8352,14 @@
       <c r="J255" t="s">
         <v>9</v>
       </c>
-      <c r="K255">
+      <c r="K255" s="1">
         <v>1</v>
       </c>
       <c r="L255" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="256" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
         <v>7</v>
       </c>
@@ -8361,7 +8378,7 @@
       <c r="J256" t="s">
         <v>9</v>
       </c>
-      <c r="K256">
+      <c r="K256" s="1">
         <v>1</v>
       </c>
       <c r="L256" t="s">
@@ -8371,7 +8388,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="257" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
         <v>7</v>
       </c>
@@ -8390,14 +8407,14 @@
       <c r="J257" t="s">
         <v>9</v>
       </c>
-      <c r="K257">
+      <c r="K257" s="1">
         <v>1</v>
       </c>
       <c r="L257" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="258" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
         <v>7</v>
       </c>
@@ -8416,14 +8433,14 @@
       <c r="J258" t="s">
         <v>9</v>
       </c>
-      <c r="K258">
+      <c r="K258" s="1">
         <v>1</v>
       </c>
       <c r="L258" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="259" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
         <v>7</v>
       </c>
@@ -8442,7 +8459,7 @@
       <c r="J259" t="s">
         <v>9</v>
       </c>
-      <c r="K259">
+      <c r="K259" s="1">
         <v>1</v>
       </c>
       <c r="L259" t="s">
@@ -8452,7 +8469,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="260" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
         <v>7</v>
       </c>
@@ -8471,14 +8488,14 @@
       <c r="J260" t="s">
         <v>9</v>
       </c>
-      <c r="K260">
+      <c r="K260" s="1">
         <v>1</v>
       </c>
       <c r="L260" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="261" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
         <v>7</v>
       </c>
@@ -8497,14 +8514,14 @@
       <c r="J261" t="s">
         <v>9</v>
       </c>
-      <c r="K261">
+      <c r="K261" s="1">
         <v>1</v>
       </c>
       <c r="L261" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="262" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
         <v>7</v>
       </c>
@@ -8523,14 +8540,14 @@
       <c r="J262" t="s">
         <v>72</v>
       </c>
-      <c r="K262">
+      <c r="K262" s="1">
         <v>1</v>
       </c>
       <c r="L262" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="263" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
         <v>7</v>
       </c>
@@ -8549,14 +8566,14 @@
       <c r="J263" t="s">
         <v>9</v>
       </c>
-      <c r="K263">
+      <c r="K263" s="1">
         <v>1</v>
       </c>
       <c r="L263" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="264" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
         <v>7</v>
       </c>
@@ -8575,14 +8592,14 @@
       <c r="J264" t="s">
         <v>34</v>
       </c>
-      <c r="K264">
+      <c r="K264" s="1">
         <v>1</v>
       </c>
       <c r="L264" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="265" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
         <v>7</v>
       </c>
@@ -8601,14 +8618,14 @@
       <c r="J265" t="s">
         <v>9</v>
       </c>
-      <c r="K265">
+      <c r="K265" s="1">
         <v>1</v>
       </c>
       <c r="L265" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="266" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
         <v>7</v>
       </c>
@@ -8627,14 +8644,14 @@
       <c r="J266" t="s">
         <v>9</v>
       </c>
-      <c r="K266">
+      <c r="K266" s="1">
         <v>1</v>
       </c>
       <c r="L266" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="267" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
         <v>7</v>
       </c>
@@ -8653,14 +8670,14 @@
       <c r="J267" t="s">
         <v>9</v>
       </c>
-      <c r="K267">
+      <c r="K267" s="1">
         <v>1</v>
       </c>
       <c r="L267" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="268" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
         <v>7</v>
       </c>
@@ -8679,14 +8696,14 @@
       <c r="J268" t="s">
         <v>9</v>
       </c>
-      <c r="K268">
+      <c r="K268" s="1">
         <v>1</v>
       </c>
       <c r="L268" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="269" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
         <v>7</v>
       </c>
@@ -8705,14 +8722,14 @@
       <c r="J269" t="s">
         <v>9</v>
       </c>
-      <c r="K269">
+      <c r="K269" s="1">
         <v>1</v>
       </c>
       <c r="L269" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="270" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
         <v>7</v>
       </c>
@@ -8731,14 +8748,14 @@
       <c r="J270" t="s">
         <v>9</v>
       </c>
-      <c r="K270">
+      <c r="K270" s="1">
         <v>1</v>
       </c>
       <c r="L270" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="271" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
         <v>7</v>
       </c>
@@ -8757,14 +8774,14 @@
       <c r="J271" t="s">
         <v>9</v>
       </c>
-      <c r="K271">
+      <c r="K271" s="1">
         <v>1</v>
       </c>
       <c r="L271" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="272" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
         <v>7</v>
       </c>
@@ -8783,14 +8800,14 @@
       <c r="J272" t="s">
         <v>9</v>
       </c>
-      <c r="K272">
+      <c r="K272" s="1">
         <v>1</v>
       </c>
       <c r="L272" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="273" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
         <v>7</v>
       </c>
@@ -8809,14 +8826,14 @@
       <c r="J273" t="s">
         <v>9</v>
       </c>
-      <c r="K273">
+      <c r="K273" s="1">
         <v>1</v>
       </c>
       <c r="L273" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="274" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
         <v>7</v>
       </c>
@@ -8835,14 +8852,14 @@
       <c r="J274" t="s">
         <v>9</v>
       </c>
-      <c r="K274">
+      <c r="K274" s="1">
         <v>1</v>
       </c>
       <c r="L274" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="275" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
         <v>7</v>
       </c>
@@ -8861,14 +8878,14 @@
       <c r="J275" t="s">
         <v>9</v>
       </c>
-      <c r="K275">
+      <c r="K275" s="1">
         <v>1</v>
       </c>
       <c r="L275" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="276" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
         <v>7</v>
       </c>
@@ -8887,14 +8904,14 @@
       <c r="J276" t="s">
         <v>9</v>
       </c>
-      <c r="K276">
+      <c r="K276" s="1">
         <v>1</v>
       </c>
       <c r="L276" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="277" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
         <v>7</v>
       </c>
@@ -8913,14 +8930,14 @@
       <c r="J277" t="s">
         <v>9</v>
       </c>
-      <c r="K277">
+      <c r="K277" s="1">
         <v>1</v>
       </c>
       <c r="L277" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="278" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
         <v>7</v>
       </c>
@@ -8939,14 +8956,14 @@
       <c r="J278" t="s">
         <v>9</v>
       </c>
-      <c r="K278">
+      <c r="K278" s="1">
         <v>1</v>
       </c>
       <c r="L278" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="279" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
         <v>7</v>
       </c>
@@ -8965,14 +8982,14 @@
       <c r="J279" t="s">
         <v>9</v>
       </c>
-      <c r="K279">
+      <c r="K279" s="1">
         <v>1</v>
       </c>
       <c r="L279" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="280" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
         <v>7</v>
       </c>
@@ -8991,14 +9008,14 @@
       <c r="J280" t="s">
         <v>34</v>
       </c>
-      <c r="K280">
+      <c r="K280" s="1">
         <v>1</v>
       </c>
       <c r="L280" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="281" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
         <v>7</v>
       </c>
@@ -9017,14 +9034,14 @@
       <c r="J281" t="s">
         <v>34</v>
       </c>
-      <c r="K281">
+      <c r="K281" s="1">
         <v>1</v>
       </c>
       <c r="L281" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="282" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
         <v>7</v>
       </c>
@@ -9043,14 +9060,14 @@
       <c r="J282" t="s">
         <v>9</v>
       </c>
-      <c r="K282">
+      <c r="K282" s="1">
         <v>1</v>
       </c>
       <c r="L282" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="283" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
         <v>7</v>
       </c>
@@ -9069,14 +9086,14 @@
       <c r="J283" t="s">
         <v>9</v>
       </c>
-      <c r="K283">
+      <c r="K283" s="1">
         <v>1</v>
       </c>
       <c r="L283" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="284" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
         <v>7</v>
       </c>
@@ -9095,14 +9112,14 @@
       <c r="J284" t="s">
         <v>9</v>
       </c>
-      <c r="K284">
+      <c r="K284" s="1">
         <v>1</v>
       </c>
       <c r="L284" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="285" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
         <v>7</v>
       </c>
@@ -9121,14 +9138,14 @@
       <c r="J285" t="s">
         <v>9</v>
       </c>
-      <c r="K285">
+      <c r="K285" s="1">
         <v>1</v>
       </c>
       <c r="L285" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="286" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
         <v>7</v>
       </c>
@@ -9147,14 +9164,14 @@
       <c r="J286" t="s">
         <v>9</v>
       </c>
-      <c r="K286">
+      <c r="K286" s="1">
         <v>1</v>
       </c>
       <c r="L286" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="287" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
         <v>7</v>
       </c>
@@ -9173,14 +9190,14 @@
       <c r="J287" t="s">
         <v>9</v>
       </c>
-      <c r="K287">
+      <c r="K287" s="1">
         <v>1</v>
       </c>
       <c r="L287" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="288" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
         <v>7</v>
       </c>
@@ -9199,14 +9216,14 @@
       <c r="J288" t="s">
         <v>9</v>
       </c>
-      <c r="K288">
+      <c r="K288" s="1">
         <v>1</v>
       </c>
       <c r="L288" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="289" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
         <v>7</v>
       </c>
@@ -9225,14 +9242,14 @@
       <c r="J289" t="s">
         <v>9</v>
       </c>
-      <c r="K289">
+      <c r="K289" s="1">
         <v>1</v>
       </c>
       <c r="L289" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="290" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
         <v>7</v>
       </c>
@@ -9251,14 +9268,14 @@
       <c r="J290" t="s">
         <v>9</v>
       </c>
-      <c r="K290">
+      <c r="K290" s="1">
         <v>1</v>
       </c>
       <c r="L290" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="291" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
         <v>7</v>
       </c>
@@ -9277,14 +9294,14 @@
       <c r="J291" t="s">
         <v>9</v>
       </c>
-      <c r="K291">
+      <c r="K291" s="1">
         <v>1</v>
       </c>
       <c r="L291" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="292" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
         <v>7</v>
       </c>
@@ -9303,14 +9320,14 @@
       <c r="J292" t="s">
         <v>9</v>
       </c>
-      <c r="K292">
+      <c r="K292" s="1">
         <v>1</v>
       </c>
       <c r="L292" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="293" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
         <v>7</v>
       </c>
@@ -9329,14 +9346,14 @@
       <c r="J293" t="s">
         <v>9</v>
       </c>
-      <c r="K293">
+      <c r="K293" s="1">
         <v>1</v>
       </c>
       <c r="L293" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="294" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
         <v>7</v>
       </c>
@@ -9355,14 +9372,14 @@
       <c r="J294" t="s">
         <v>9</v>
       </c>
-      <c r="K294">
+      <c r="K294" s="1">
         <v>1</v>
       </c>
       <c r="L294" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="295" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
         <v>7</v>
       </c>
@@ -9381,14 +9398,14 @@
       <c r="J295" t="s">
         <v>9</v>
       </c>
-      <c r="K295">
+      <c r="K295" s="1">
         <v>1</v>
       </c>
       <c r="L295" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="296" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
         <v>7</v>
       </c>
@@ -9407,14 +9424,14 @@
       <c r="J296" t="s">
         <v>9</v>
       </c>
-      <c r="K296">
+      <c r="K296" s="1">
         <v>1</v>
       </c>
       <c r="L296" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="297" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
         <v>7</v>
       </c>
@@ -9433,14 +9450,14 @@
       <c r="J297" t="s">
         <v>9</v>
       </c>
-      <c r="K297">
+      <c r="K297" s="1">
         <v>1</v>
       </c>
       <c r="L297" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="298" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
         <v>7</v>
       </c>
@@ -9459,14 +9476,14 @@
       <c r="J298" t="s">
         <v>9</v>
       </c>
-      <c r="K298">
+      <c r="K298" s="1">
         <v>1</v>
       </c>
       <c r="L298" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="299" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
         <v>7</v>
       </c>
@@ -9485,14 +9502,14 @@
       <c r="J299" t="s">
         <v>9</v>
       </c>
-      <c r="K299">
+      <c r="K299" s="1">
         <v>1</v>
       </c>
       <c r="L299" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="300" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
         <v>7</v>
       </c>
@@ -9511,14 +9528,14 @@
       <c r="J300" t="s">
         <v>9</v>
       </c>
-      <c r="K300">
+      <c r="K300" s="1">
         <v>1</v>
       </c>
       <c r="L300" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="301" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
         <v>7</v>
       </c>
@@ -9537,14 +9554,14 @@
       <c r="J301" t="s">
         <v>9</v>
       </c>
-      <c r="K301">
+      <c r="K301" s="1">
         <v>1</v>
       </c>
       <c r="L301" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="302" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
         <v>7</v>
       </c>
@@ -9563,14 +9580,14 @@
       <c r="J302" t="s">
         <v>9</v>
       </c>
-      <c r="K302">
+      <c r="K302" s="1">
         <v>1</v>
       </c>
       <c r="L302" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="303" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
         <v>7</v>
       </c>
@@ -9589,14 +9606,14 @@
       <c r="J303" t="s">
         <v>9</v>
       </c>
-      <c r="K303">
+      <c r="K303" s="1">
         <v>1</v>
       </c>
       <c r="L303" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="304" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
         <v>7</v>
       </c>
@@ -9615,14 +9632,14 @@
       <c r="J304" t="s">
         <v>9</v>
       </c>
-      <c r="K304">
+      <c r="K304" s="1">
         <v>1</v>
       </c>
       <c r="L304" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="305" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
         <v>7</v>
       </c>
@@ -9641,14 +9658,14 @@
       <c r="J305" t="s">
         <v>34</v>
       </c>
-      <c r="K305">
+      <c r="K305" s="1">
         <v>1</v>
       </c>
       <c r="L305" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="306" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
         <v>7</v>
       </c>
@@ -9667,14 +9684,14 @@
       <c r="J306" t="s">
         <v>9</v>
       </c>
-      <c r="K306">
+      <c r="K306" s="1">
         <v>1</v>
       </c>
       <c r="L306" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="307" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
         <v>7</v>
       </c>
@@ -9693,14 +9710,14 @@
       <c r="J307" t="s">
         <v>9</v>
       </c>
-      <c r="K307">
+      <c r="K307" s="1">
         <v>1</v>
       </c>
       <c r="L307" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="308" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
         <v>7</v>
       </c>
@@ -9719,14 +9736,14 @@
       <c r="J308" t="s">
         <v>9</v>
       </c>
-      <c r="K308">
+      <c r="K308" s="1">
         <v>1</v>
       </c>
       <c r="L308" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="309" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
         <v>7</v>
       </c>
@@ -9745,14 +9762,14 @@
       <c r="J309" t="s">
         <v>9</v>
       </c>
-      <c r="K309">
+      <c r="K309" s="1">
         <v>1</v>
       </c>
       <c r="L309" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="310" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
         <v>7</v>
       </c>
@@ -9771,14 +9788,14 @@
       <c r="J310" t="s">
         <v>9</v>
       </c>
-      <c r="K310">
+      <c r="K310" s="1">
         <v>1</v>
       </c>
       <c r="L310" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="311" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
         <v>7</v>
       </c>
@@ -9797,14 +9814,14 @@
       <c r="J311" t="s">
         <v>9</v>
       </c>
-      <c r="K311">
+      <c r="K311" s="1">
         <v>1</v>
       </c>
       <c r="L311" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="312" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
         <v>7</v>
       </c>
@@ -9823,14 +9840,14 @@
       <c r="J312" t="s">
         <v>9</v>
       </c>
-      <c r="K312">
+      <c r="K312" s="1">
         <v>1</v>
       </c>
       <c r="L312" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="313" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
         <v>7</v>
       </c>
@@ -9849,14 +9866,14 @@
       <c r="J313" t="s">
         <v>9</v>
       </c>
-      <c r="K313">
+      <c r="K313" s="1">
         <v>1</v>
       </c>
       <c r="L313" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="314" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
         <v>7</v>
       </c>
@@ -9875,14 +9892,14 @@
       <c r="J314" t="s">
         <v>9</v>
       </c>
-      <c r="K314">
+      <c r="K314" s="1">
         <v>1</v>
       </c>
       <c r="L314" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="315" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
         <v>7</v>
       </c>
@@ -9901,14 +9918,14 @@
       <c r="J315" t="s">
         <v>9</v>
       </c>
-      <c r="K315">
+      <c r="K315" s="1">
         <v>1</v>
       </c>
       <c r="L315" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="316" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
         <v>7</v>
       </c>
@@ -9927,14 +9944,14 @@
       <c r="J316" t="s">
         <v>9</v>
       </c>
-      <c r="K316">
+      <c r="K316" s="1">
         <v>1</v>
       </c>
       <c r="L316" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="317" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
         <v>7</v>
       </c>
@@ -9953,14 +9970,14 @@
       <c r="J317" t="s">
         <v>9</v>
       </c>
-      <c r="K317">
+      <c r="K317" s="1">
         <v>1</v>
       </c>
       <c r="L317" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="318" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
         <v>7</v>
       </c>
@@ -9979,14 +9996,14 @@
       <c r="J318" t="s">
         <v>9</v>
       </c>
-      <c r="K318">
+      <c r="K318" s="1">
         <v>1</v>
       </c>
       <c r="L318" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="319" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
         <v>7</v>
       </c>
@@ -10005,14 +10022,14 @@
       <c r="J319" t="s">
         <v>9</v>
       </c>
-      <c r="K319">
+      <c r="K319" s="1">
         <v>1</v>
       </c>
       <c r="L319" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="320" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
         <v>7</v>
       </c>
@@ -10031,14 +10048,14 @@
       <c r="J320" t="s">
         <v>9</v>
       </c>
-      <c r="K320">
+      <c r="K320" s="1">
         <v>1</v>
       </c>
       <c r="L320" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="321" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
         <v>7</v>
       </c>
@@ -10057,14 +10074,14 @@
       <c r="J321" t="s">
         <v>9</v>
       </c>
-      <c r="K321">
+      <c r="K321" s="1">
         <v>1</v>
       </c>
       <c r="L321" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="322" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
         <v>7</v>
       </c>
@@ -10083,14 +10100,14 @@
       <c r="J322" t="s">
         <v>9</v>
       </c>
-      <c r="K322">
+      <c r="K322" s="1">
         <v>1</v>
       </c>
       <c r="L322" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="323" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
         <v>7</v>
       </c>
@@ -10109,14 +10126,14 @@
       <c r="J323" t="s">
         <v>9</v>
       </c>
-      <c r="K323">
+      <c r="K323" s="1">
         <v>1</v>
       </c>
       <c r="L323" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="324" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
         <v>7</v>
       </c>
@@ -10135,14 +10152,14 @@
       <c r="J324" t="s">
         <v>9</v>
       </c>
-      <c r="K324">
+      <c r="K324" s="1">
         <v>1</v>
       </c>
       <c r="L324" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="325" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
         <v>7</v>
       </c>
@@ -10161,14 +10178,14 @@
       <c r="J325" t="s">
         <v>9</v>
       </c>
-      <c r="K325">
+      <c r="K325" s="1">
         <v>1</v>
       </c>
       <c r="L325" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="326" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
         <v>7</v>
       </c>
@@ -10187,14 +10204,14 @@
       <c r="J326" t="s">
         <v>9</v>
       </c>
-      <c r="K326">
+      <c r="K326" s="1">
         <v>1</v>
       </c>
       <c r="L326" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="327" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
         <v>7</v>
       </c>
@@ -10213,7 +10230,7 @@
       <c r="J327" t="s">
         <v>9</v>
       </c>
-      <c r="K327">
+      <c r="K327" s="1">
         <v>1</v>
       </c>
       <c r="L327" t="s">
@@ -10223,7 +10240,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="328" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
         <v>7</v>
       </c>
@@ -10242,7 +10259,7 @@
       <c r="J328" t="s">
         <v>9</v>
       </c>
-      <c r="K328">
+      <c r="K328" s="1">
         <v>1</v>
       </c>
       <c r="L328" t="s">
@@ -10252,7 +10269,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="329" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
         <v>7</v>
       </c>
@@ -10271,14 +10288,14 @@
       <c r="J329" t="s">
         <v>9</v>
       </c>
-      <c r="K329">
+      <c r="K329" s="1">
         <v>1</v>
       </c>
       <c r="L329" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="330" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
         <v>7</v>
       </c>
@@ -10297,14 +10314,14 @@
       <c r="J330" t="s">
         <v>9</v>
       </c>
-      <c r="K330">
+      <c r="K330" s="1">
         <v>1</v>
       </c>
       <c r="L330" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="331" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
         <v>7</v>
       </c>
@@ -10323,14 +10340,14 @@
       <c r="J331" t="s">
         <v>9</v>
       </c>
-      <c r="K331">
+      <c r="K331" s="1">
         <v>1</v>
       </c>
       <c r="L331" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="332" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
         <v>7</v>
       </c>
@@ -10349,14 +10366,14 @@
       <c r="J332" t="s">
         <v>9</v>
       </c>
-      <c r="K332">
+      <c r="K332" s="1">
         <v>1</v>
       </c>
       <c r="L332" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="333" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
         <v>7</v>
       </c>
@@ -10375,14 +10392,14 @@
       <c r="J333" t="s">
         <v>9</v>
       </c>
-      <c r="K333">
+      <c r="K333" s="1">
         <v>1</v>
       </c>
       <c r="L333" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="334" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
         <v>7</v>
       </c>
@@ -10401,14 +10418,14 @@
       <c r="J334" t="s">
         <v>9</v>
       </c>
-      <c r="K334">
+      <c r="K334" s="1">
         <v>1</v>
       </c>
       <c r="L334" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="335" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
         <v>7</v>
       </c>
@@ -10427,14 +10444,14 @@
       <c r="J335" t="s">
         <v>9</v>
       </c>
-      <c r="K335">
+      <c r="K335" s="1">
         <v>1</v>
       </c>
       <c r="L335" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="336" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
         <v>7</v>
       </c>
@@ -10453,14 +10470,14 @@
       <c r="J336" t="s">
         <v>9</v>
       </c>
-      <c r="K336">
+      <c r="K336" s="1">
         <v>1</v>
       </c>
       <c r="L336" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="337" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
         <v>7</v>
       </c>
@@ -10479,14 +10496,14 @@
       <c r="J337" t="s">
         <v>9</v>
       </c>
-      <c r="K337">
+      <c r="K337" s="1">
         <v>1</v>
       </c>
       <c r="L337" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="338" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
         <v>7</v>
       </c>
@@ -10505,14 +10522,14 @@
       <c r="J338" t="s">
         <v>9</v>
       </c>
-      <c r="K338">
+      <c r="K338" s="1">
         <v>1</v>
       </c>
       <c r="L338" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="339" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
         <v>7</v>
       </c>
@@ -10531,14 +10548,14 @@
       <c r="J339" t="s">
         <v>9</v>
       </c>
-      <c r="K339">
+      <c r="K339" s="1">
         <v>1</v>
       </c>
       <c r="L339" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="340" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
         <v>7</v>
       </c>
@@ -10557,14 +10574,14 @@
       <c r="J340" t="s">
         <v>9</v>
       </c>
-      <c r="K340">
+      <c r="K340" s="1">
         <v>1</v>
       </c>
       <c r="L340" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="341" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
         <v>7</v>
       </c>
@@ -10583,14 +10600,14 @@
       <c r="J341" t="s">
         <v>9</v>
       </c>
-      <c r="K341">
+      <c r="K341" s="1">
         <v>1</v>
       </c>
       <c r="L341" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="342" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
         <v>7</v>
       </c>
@@ -10609,14 +10626,14 @@
       <c r="J342" t="s">
         <v>9</v>
       </c>
-      <c r="K342">
+      <c r="K342" s="1">
         <v>1</v>
       </c>
       <c r="L342" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="343" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
         <v>7</v>
       </c>
@@ -10635,14 +10652,14 @@
       <c r="J343" t="s">
         <v>9</v>
       </c>
-      <c r="K343">
+      <c r="K343" s="1">
         <v>1</v>
       </c>
       <c r="L343" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="344" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
         <v>7</v>
       </c>
@@ -10661,14 +10678,14 @@
       <c r="J344" t="s">
         <v>9</v>
       </c>
-      <c r="K344">
+      <c r="K344" s="1">
         <v>1</v>
       </c>
       <c r="L344" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="345" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
         <v>7</v>
       </c>
@@ -10687,14 +10704,14 @@
       <c r="J345" t="s">
         <v>9</v>
       </c>
-      <c r="K345">
+      <c r="K345" s="1">
         <v>1</v>
       </c>
       <c r="L345" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="346" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
         <v>7</v>
       </c>
@@ -10713,14 +10730,14 @@
       <c r="J346" t="s">
         <v>9</v>
       </c>
-      <c r="K346">
+      <c r="K346" s="1">
         <v>1</v>
       </c>
       <c r="L346" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="347" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
         <v>7</v>
       </c>
@@ -10739,14 +10756,14 @@
       <c r="J347" t="s">
         <v>9</v>
       </c>
-      <c r="K347">
+      <c r="K347" s="1">
         <v>1</v>
       </c>
       <c r="L347" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="348" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
         <v>7</v>
       </c>
@@ -10765,14 +10782,14 @@
       <c r="J348" t="s">
         <v>9</v>
       </c>
-      <c r="K348">
+      <c r="K348" s="1">
         <v>1</v>
       </c>
       <c r="L348" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="349" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
         <v>7</v>
       </c>
@@ -10791,14 +10808,14 @@
       <c r="J349" t="s">
         <v>9</v>
       </c>
-      <c r="K349">
+      <c r="K349" s="1">
         <v>1</v>
       </c>
       <c r="L349" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="350" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
         <v>7</v>
       </c>
@@ -10817,14 +10834,14 @@
       <c r="J350" t="s">
         <v>9</v>
       </c>
-      <c r="K350">
+      <c r="K350" s="1">
         <v>1</v>
       </c>
       <c r="L350" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="351" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
         <v>7</v>
       </c>
@@ -10843,14 +10860,14 @@
       <c r="J351" t="s">
         <v>9</v>
       </c>
-      <c r="K351">
+      <c r="K351" s="1">
         <v>1</v>
       </c>
       <c r="L351" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="352" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
         <v>7</v>
       </c>
@@ -10869,14 +10886,14 @@
       <c r="J352" t="s">
         <v>9</v>
       </c>
-      <c r="K352">
+      <c r="K352" s="1">
         <v>1</v>
       </c>
       <c r="L352" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="353" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
         <v>7</v>
       </c>
@@ -10895,14 +10912,14 @@
       <c r="J353" t="s">
         <v>9</v>
       </c>
-      <c r="K353">
+      <c r="K353" s="1">
         <v>1</v>
       </c>
       <c r="L353" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="354" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
         <v>7</v>
       </c>
@@ -10921,14 +10938,14 @@
       <c r="J354" t="s">
         <v>9</v>
       </c>
-      <c r="K354">
+      <c r="K354" s="1">
         <v>1</v>
       </c>
       <c r="L354" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="355" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
         <v>7</v>
       </c>
@@ -10947,14 +10964,14 @@
       <c r="J355" t="s">
         <v>9</v>
       </c>
-      <c r="K355">
+      <c r="K355" s="1">
         <v>1</v>
       </c>
       <c r="L355" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="356" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
         <v>7</v>
       </c>
@@ -10973,14 +10990,14 @@
       <c r="J356" t="s">
         <v>9</v>
       </c>
-      <c r="K356">
+      <c r="K356" s="1">
         <v>1</v>
       </c>
       <c r="L356" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="357" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
         <v>7</v>
       </c>
@@ -10999,14 +11016,14 @@
       <c r="J357" t="s">
         <v>9</v>
       </c>
-      <c r="K357">
+      <c r="K357" s="1">
         <v>1</v>
       </c>
       <c r="L357" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="358" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
         <v>7</v>
       </c>
@@ -11025,14 +11042,14 @@
       <c r="J358" t="s">
         <v>9</v>
       </c>
-      <c r="K358">
+      <c r="K358" s="1">
         <v>1</v>
       </c>
       <c r="L358" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="359" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
         <v>7</v>
       </c>
@@ -11051,14 +11068,14 @@
       <c r="J359" t="s">
         <v>9</v>
       </c>
-      <c r="K359">
+      <c r="K359" s="1">
         <v>1</v>
       </c>
       <c r="L359" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="360" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
         <v>7</v>
       </c>
@@ -11077,14 +11094,14 @@
       <c r="J360" t="s">
         <v>9</v>
       </c>
-      <c r="K360">
+      <c r="K360" s="1">
         <v>1</v>
       </c>
       <c r="L360" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="361" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
         <v>7</v>
       </c>
@@ -11103,14 +11120,14 @@
       <c r="J361" t="s">
         <v>9</v>
       </c>
-      <c r="K361">
+      <c r="K361" s="1">
         <v>1</v>
       </c>
       <c r="L361" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="362" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
         <v>7</v>
       </c>
@@ -11129,14 +11146,14 @@
       <c r="J362" t="s">
         <v>9</v>
       </c>
-      <c r="K362">
+      <c r="K362" s="1">
         <v>1</v>
       </c>
       <c r="L362" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="363" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
         <v>7</v>
       </c>
@@ -11155,14 +11172,14 @@
       <c r="J363" t="s">
         <v>9</v>
       </c>
-      <c r="K363">
+      <c r="K363" s="1">
         <v>1</v>
       </c>
       <c r="L363" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="364" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
         <v>7</v>
       </c>
@@ -11181,14 +11198,14 @@
       <c r="J364" t="s">
         <v>9</v>
       </c>
-      <c r="K364">
+      <c r="K364" s="1">
         <v>1</v>
       </c>
       <c r="L364" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="365" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
         <v>7</v>
       </c>
@@ -11207,14 +11224,14 @@
       <c r="J365" t="s">
         <v>9</v>
       </c>
-      <c r="K365">
+      <c r="K365" s="1">
         <v>1</v>
       </c>
       <c r="L365" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="366" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
         <v>7</v>
       </c>
@@ -11233,14 +11250,14 @@
       <c r="J366" t="s">
         <v>9</v>
       </c>
-      <c r="K366">
+      <c r="K366" s="1">
         <v>1</v>
       </c>
       <c r="L366" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="367" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
         <v>7</v>
       </c>
@@ -11259,14 +11276,14 @@
       <c r="J367" t="s">
         <v>9</v>
       </c>
-      <c r="K367">
+      <c r="K367" s="1">
         <v>1</v>
       </c>
       <c r="L367" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="368" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
         <v>7</v>
       </c>
@@ -11285,14 +11302,14 @@
       <c r="J368" t="s">
         <v>9</v>
       </c>
-      <c r="K368">
+      <c r="K368" s="1">
         <v>1</v>
       </c>
       <c r="L368" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="369" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
         <v>7</v>
       </c>
@@ -11311,14 +11328,14 @@
       <c r="J369" t="s">
         <v>9</v>
       </c>
-      <c r="K369">
+      <c r="K369" s="1">
         <v>1</v>
       </c>
       <c r="L369" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="370" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
         <v>7</v>
       </c>
@@ -11337,14 +11354,14 @@
       <c r="J370" t="s">
         <v>9</v>
       </c>
-      <c r="K370">
+      <c r="K370" s="1">
         <v>1</v>
       </c>
       <c r="L370" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="371" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
         <v>7</v>
       </c>
@@ -11363,14 +11380,14 @@
       <c r="J371" t="s">
         <v>9</v>
       </c>
-      <c r="K371">
+      <c r="K371" s="1">
         <v>1</v>
       </c>
       <c r="L371" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="372" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
         <v>7</v>
       </c>
@@ -11389,14 +11406,14 @@
       <c r="J372" t="s">
         <v>9</v>
       </c>
-      <c r="K372">
+      <c r="K372" s="1">
         <v>1</v>
       </c>
       <c r="L372" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="373" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
         <v>7</v>
       </c>
@@ -11415,7 +11432,7 @@
       <c r="J373" t="s">
         <v>9</v>
       </c>
-      <c r="K373">
+      <c r="K373" s="1">
         <v>1</v>
       </c>
       <c r="L373" t="s">
@@ -11423,6 +11440,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <extLst>
